--- a/ValueSet-HIV.D.DE457.xlsx
+++ b/ValueSet-HIV.D.DE457.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-02T03:11:41+00:00</t>
+    <t>2025-03-13T17:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE457.xlsx
+++ b/ValueSet-HIV.D.DE457.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T17:17:21+00:00</t>
+    <t>2025-03-13T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.D.DE457.xlsx
+++ b/ValueSet-HIV.D.DE457.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T17:18:21+00:00</t>
+    <t>2025-03-14T13:53:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
